--- a/artfynd/A 30608-2025 artfynd.xlsx
+++ b/artfynd/A 30608-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121279353</v>
+        <v>121279347</v>
       </c>
       <c r="B2" t="n">
-        <v>79695</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99800</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>260</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myrstarr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carex heleonastes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Ehrh. ex L.f.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>687580</v>
+        <v>687533</v>
       </c>
       <c r="R2" t="n">
-        <v>7138234</v>
+        <v>7138315</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121279354</v>
+        <v>121279353</v>
       </c>
       <c r="B3" t="n">
-        <v>79695</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,7 +811,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687582</v>
+        <v>687580</v>
       </c>
       <c r="R3" t="n">
         <v>7138234</v>
@@ -880,6 +870,212 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121279354</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hundliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>687582</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7138234</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elin Lindén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elin Lindén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121279348</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hundliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>687538</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7138307</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Lindén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elin Lindén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 30608-2025 artfynd.xlsx
+++ b/artfynd/A 30608-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121279347</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121279353</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121279354</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,8 +1100,19 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121279348</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>